--- a/config/Excel/Zones.xlsx
+++ b/config/Excel/Zones.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="地圖" sheetId="1" r:id="R1f38118d6de74afc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="地圖" sheetId="1" r:id="Rc26318a6ce1d4c3b"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -153,8 +153,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="ZonesTable" displayName="ZonesTable" ref="A1:H8" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:tableColumns count="8">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="ZonesTable" displayName="ZonesTable" ref="A1:M8" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:tableColumns count="13">
     <x:tableColumn id="1" name="順序"/>
     <x:tableColumn id="2" name="地圖識別碼"/>
     <x:tableColumn id="3" name="地圖名稱"/>
@@ -163,6 +163,11 @@
     <x:tableColumn id="6" name="前置地圖識別碼"/>
     <x:tableColumn id="7" name="前置通關關卡"/>
     <x:tableColumn id="8" name="最低轉生次數"/>
+    <x:tableColumn id="9" name="生命倍率"/>
+    <x:tableColumn id="10" name="攻擊倍率"/>
+    <x:tableColumn id="11" name="防禦倍率"/>
+    <x:tableColumn id="12" name="攻速倍率"/>
+    <x:tableColumn id="13" name="經驗金幣獎勵倍率"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
@@ -371,6 +376,11 @@
     <x:col min="6" max="6" width="22" hidden="0" customWidth="1"/>
     <x:col min="7" max="7" width="18" hidden="0" customWidth="1"/>
     <x:col min="8" max="8" width="16" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="14" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="14" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="14" hidden="0" customWidth="1"/>
+    <x:col min="12" max="12" width="14" hidden="0" customWidth="1"/>
+    <x:col min="13" max="13" width="20" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -398,6 +408,21 @@
       <x:c r="H1" s="14" t="str">
         <x:v>最低轉生次數</x:v>
       </x:c>
+      <x:c r="I1" s="14" t="str">
+        <x:v>生命倍率</x:v>
+      </x:c>
+      <x:c r="J1" s="14" t="str">
+        <x:v>攻擊倍率</x:v>
+      </x:c>
+      <x:c r="K1" s="14" t="str">
+        <x:v>防禦倍率</x:v>
+      </x:c>
+      <x:c r="L1" s="14" t="str">
+        <x:v>攻速倍率</x:v>
+      </x:c>
+      <x:c r="M1" s="14" t="str">
+        <x:v>經驗金幣獎勵倍率</x:v>
+      </x:c>
     </x:row>
     <x:row r="2" ht="15" hidden="0" customHeight="1">
       <x:c r="A2" s="20" t="str">
@@ -420,6 +445,21 @@
       <x:c r="H2" s="18" t="str">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="I2" s="18" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J2" s="18" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K2" s="18" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L2" s="18" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M2" s="18" t="str">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="3" ht="15" hidden="0" customHeight="1">
       <x:c r="A3" s="20" t="str">
@@ -446,6 +486,21 @@
       <x:c r="H3" s="18" t="str">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="I3" s="18" t="str">
+        <x:v>2.2</x:v>
+      </x:c>
+      <x:c r="J3" s="18" t="str">
+        <x:v>1.8</x:v>
+      </x:c>
+      <x:c r="K3" s="18" t="str">
+        <x:v>1.6</x:v>
+      </x:c>
+      <x:c r="L3" s="18" t="str">
+        <x:v>1.5</x:v>
+      </x:c>
+      <x:c r="M3" s="18" t="str">
+        <x:v>1.25</x:v>
+      </x:c>
     </x:row>
     <x:row r="4" ht="15" hidden="0" customHeight="1">
       <x:c r="A4" s="20" t="str">
@@ -472,6 +527,21 @@
       <x:c r="H4" s="18" t="str">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="I4" s="18" t="str">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="J4" s="18" t="str">
+        <x:v>2.8</x:v>
+      </x:c>
+      <x:c r="K4" s="18" t="str">
+        <x:v>2.4</x:v>
+      </x:c>
+      <x:c r="L4" s="18" t="str">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="M4" s="18" t="str">
+        <x:v>1.5</x:v>
+      </x:c>
     </x:row>
     <x:row r="5" ht="15" hidden="0" customHeight="1">
       <x:c r="A5" s="20" t="str">
@@ -498,6 +568,21 @@
       <x:c r="H5" s="18" t="str">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="I5" s="18" t="str">
+        <x:v>6.5</x:v>
+      </x:c>
+      <x:c r="J5" s="18" t="str">
+        <x:v>3.8</x:v>
+      </x:c>
+      <x:c r="K5" s="18" t="str">
+        <x:v>3.2</x:v>
+      </x:c>
+      <x:c r="L5" s="18" t="str">
+        <x:v>1.8</x:v>
+      </x:c>
+      <x:c r="M5" s="18" t="str">
+        <x:v>2.25</x:v>
+      </x:c>
     </x:row>
     <x:row r="6" ht="15" hidden="0" customHeight="1">
       <x:c r="A6" s="20" t="str">
@@ -524,6 +609,21 @@
       <x:c r="H6" s="18" t="str">
         <x:v>11</x:v>
       </x:c>
+      <x:c r="I6" s="18" t="str">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="J6" s="18" t="str">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="K6" s="18" t="str">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="L6" s="18" t="str">
+        <x:v>1.75</x:v>
+      </x:c>
+      <x:c r="M6" s="18" t="str">
+        <x:v>4</x:v>
+      </x:c>
     </x:row>
     <x:row r="7" ht="15" hidden="0" customHeight="1">
       <x:c r="A7" s="20" t="str">
@@ -550,6 +650,21 @@
       <x:c r="H7" s="18" t="str">
         <x:v>11</x:v>
       </x:c>
+      <x:c r="I7" s="18" t="str">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="J7" s="18" t="str">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="K7" s="18" t="str">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="L7" s="18" t="str">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="M7" s="18" t="str">
+        <x:v>10</x:v>
+      </x:c>
     </x:row>
     <x:row r="8" ht="15" hidden="0" customHeight="1">
       <x:c r="A8" s="20" t="str">
@@ -576,11 +691,26 @@
       <x:c r="H8" s="18" t="str">
         <x:v>11</x:v>
       </x:c>
+      <x:c r="I8" s="18" t="str">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="J8" s="18" t="str">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="K8" s="18" t="str">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="L8" s="18" t="str">
+        <x:v>2.25</x:v>
+      </x:c>
+      <x:c r="M8" s="18" t="str">
+        <x:v>24</x:v>
+      </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R636f7c6efe1b4169"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb1e93e0c1d6b4735"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/config/Excel/Zones.xlsx
+++ b/config/Excel/Zones.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="地圖" sheetId="1" r:id="Rc26318a6ce1d4c3b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="地圖" sheetId="1" r:id="Rc78b50d96bbd4cd3"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -710,7 +710,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb1e93e0c1d6b4735"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc3e0648261884aa5"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/config/Excel/Zones.xlsx
+++ b/config/Excel/Zones.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="地圖" sheetId="1" r:id="Rc78b50d96bbd4cd3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="地圖" sheetId="1" r:id="Ref105f094ab342ee"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -710,7 +710,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc3e0648261884aa5"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R824501bcf1cc4571"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/config/Excel/Zones.xlsx
+++ b/config/Excel/Zones.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MyGame\Idle-RPG\antigravity\config\Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MyGame\Idle-RPG\claude\config\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3AEB873F-8B9C-4211-A472-A2573E7A5B34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE431FE1-8283-462F-8473-ED1E8C343B66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="37">
   <si>
     <t>順序</t>
   </si>
@@ -80,9 +80,6 @@
     <t>plains</t>
   </si>
   <si>
-    <t>草原</t>
-  </si>
-  <si>
     <t>human</t>
   </si>
   <si>
@@ -141,13 +138,20 @@
   </si>
   <si>
     <t>永恒神域</t>
+  </si>
+  <si>
+    <t>Icefield</t>
+  </si>
+  <si>
+    <t>冰原</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
@@ -166,6 +170,12 @@
       <sz val="9"/>
       <name val="細明體"/>
       <family val="3"/>
+      <charset val="136"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="微軟正黑體"/>
+      <family val="2"/>
       <charset val="136"/>
     </font>
   </fonts>
@@ -210,7 +220,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -221,14 +231,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -604,281 +611,281 @@
         <v>13</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C2" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D2" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="D2" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="E2" s="4">
+      <c r="E2" s="2">
         <v>200</v>
       </c>
       <c r="F2" s="2"/>
-      <c r="G2" s="5"/>
-      <c r="H2" s="6">
+      <c r="G2" s="4"/>
+      <c r="H2" s="4">
         <v>0</v>
       </c>
-      <c r="I2" s="6">
+      <c r="I2" s="4">
         <v>1</v>
       </c>
-      <c r="J2" s="6">
+      <c r="J2" s="4">
         <v>1</v>
       </c>
-      <c r="K2" s="6">
+      <c r="K2" s="4">
         <v>1</v>
       </c>
-      <c r="L2" s="6">
+      <c r="L2" s="4">
         <v>1</v>
       </c>
-      <c r="M2" s="6">
+      <c r="M2" s="4">
         <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:13" ht="15" customHeight="1">
       <c r="A3" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E3" s="2">
+        <v>300</v>
+      </c>
+      <c r="F3" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="B3" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="E3" s="4">
-        <v>300</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="G3" s="6">
+      <c r="G3" s="4">
         <v>200</v>
       </c>
-      <c r="H3" s="6">
+      <c r="H3" s="4">
         <v>0</v>
       </c>
-      <c r="I3" s="6">
+      <c r="I3" s="4">
         <v>2.2000000000000002</v>
       </c>
-      <c r="J3" s="6">
+      <c r="J3" s="4">
         <v>1.8</v>
       </c>
-      <c r="K3" s="6">
+      <c r="K3" s="4">
         <v>1.6</v>
       </c>
-      <c r="L3" s="6">
+      <c r="L3" s="4">
         <v>1.4</v>
       </c>
-      <c r="M3" s="6">
+      <c r="M3" s="4">
         <v>1.2</v>
       </c>
     </row>
     <row r="4" spans="1:13" ht="15" customHeight="1">
       <c r="A4" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="C4" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="C4" s="2" t="s">
-        <v>22</v>
-      </c>
       <c r="D4" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="E4" s="4">
+        <v>15</v>
+      </c>
+      <c r="E4" s="2">
         <v>400</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="G4" s="6">
+        <v>35</v>
+      </c>
+      <c r="G4" s="4">
         <v>300</v>
       </c>
-      <c r="H4" s="6">
+      <c r="H4" s="4">
         <v>0</v>
       </c>
-      <c r="I4" s="6">
+      <c r="I4" s="4">
         <v>4.4000000000000004</v>
       </c>
-      <c r="J4" s="6">
+      <c r="J4" s="4">
         <v>2.8</v>
       </c>
-      <c r="K4" s="6">
+      <c r="K4" s="4">
         <v>2.4</v>
       </c>
-      <c r="L4" s="6">
+      <c r="L4" s="4">
         <v>1.6</v>
       </c>
-      <c r="M4" s="6">
+      <c r="M4" s="4">
         <v>1.5</v>
       </c>
     </row>
     <row r="5" spans="1:13" ht="15" customHeight="1">
       <c r="A5" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B5" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="C5" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="C5" s="2" t="s">
-        <v>25</v>
-      </c>
       <c r="D5" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="E5" s="4">
+        <v>15</v>
+      </c>
+      <c r="E5" s="2">
         <v>500</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="G5" s="6">
+        <v>20</v>
+      </c>
+      <c r="G5" s="4">
         <v>400</v>
       </c>
-      <c r="H5" s="6">
+      <c r="H5" s="4">
         <v>0</v>
       </c>
-      <c r="I5" s="6">
+      <c r="I5" s="4">
         <v>6.5</v>
       </c>
-      <c r="J5" s="6">
+      <c r="J5" s="4">
         <v>3.8</v>
       </c>
-      <c r="K5" s="6">
+      <c r="K5" s="4">
         <v>3.2</v>
       </c>
-      <c r="L5" s="6">
+      <c r="L5" s="4">
         <v>1.8</v>
       </c>
-      <c r="M5" s="6">
+      <c r="M5" s="4">
         <v>2.25</v>
       </c>
     </row>
     <row r="6" spans="1:13" ht="15" customHeight="1">
       <c r="A6" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="C6" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="D6" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="D6" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="E6" s="4">
+      <c r="E6" s="2">
         <v>600</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="G6" s="6">
+        <v>23</v>
+      </c>
+      <c r="G6" s="4">
         <v>500</v>
       </c>
-      <c r="H6" s="6">
+      <c r="H6" s="4">
         <v>11</v>
       </c>
-      <c r="I6" s="6">
+      <c r="I6" s="4">
         <v>10</v>
       </c>
-      <c r="J6" s="6">
+      <c r="J6" s="4">
         <v>5</v>
       </c>
-      <c r="K6" s="6">
+      <c r="K6" s="4">
         <v>4</v>
       </c>
-      <c r="L6" s="6">
+      <c r="L6" s="4">
         <v>2</v>
       </c>
-      <c r="M6" s="6">
+      <c r="M6" s="4">
         <v>4</v>
       </c>
     </row>
     <row r="7" spans="1:13" ht="15" customHeight="1">
       <c r="A7" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B7" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="C7" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="C7" s="2" t="s">
-        <v>32</v>
-      </c>
       <c r="D7" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="E7" s="4">
+        <v>28</v>
+      </c>
+      <c r="E7" s="2">
         <v>700</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="G7" s="6">
+        <v>26</v>
+      </c>
+      <c r="G7" s="4">
         <v>600</v>
       </c>
-      <c r="H7" s="6">
+      <c r="H7" s="4">
         <v>11</v>
       </c>
-      <c r="I7" s="6">
+      <c r="I7" s="4">
         <v>25</v>
       </c>
-      <c r="J7" s="6">
+      <c r="J7" s="4">
         <v>10</v>
       </c>
-      <c r="K7" s="6">
+      <c r="K7" s="4">
         <v>8</v>
       </c>
-      <c r="L7" s="6">
+      <c r="L7" s="4">
         <v>2.2000000000000002</v>
       </c>
-      <c r="M7" s="6">
+      <c r="M7" s="4">
         <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:13" ht="15" customHeight="1">
       <c r="A8" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="B8" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="C8" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="C8" s="2" t="s">
-        <v>35</v>
-      </c>
       <c r="D8" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="E8" s="4">
+        <v>28</v>
+      </c>
+      <c r="E8" s="2">
         <v>800</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="G8" s="6">
+        <v>30</v>
+      </c>
+      <c r="G8" s="4">
         <v>700</v>
       </c>
-      <c r="H8" s="6">
+      <c r="H8" s="4">
         <v>11</v>
       </c>
-      <c r="I8" s="6">
+      <c r="I8" s="4">
         <v>60</v>
       </c>
-      <c r="J8" s="6">
+      <c r="J8" s="4">
         <v>20</v>
       </c>
-      <c r="K8" s="6">
+      <c r="K8" s="4">
         <v>15</v>
       </c>
-      <c r="L8" s="6">
+      <c r="L8" s="4">
         <v>2.5</v>
       </c>
-      <c r="M8" s="6">
+      <c r="M8" s="4">
         <v>24</v>
       </c>
     </row>

--- a/config/Excel/Zones.xlsx
+++ b/config/Excel/Zones.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MyGame\Idle-RPG\claude\config\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE431FE1-8283-462F-8473-ED1E8C343B66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9028C24C-2A1D-4702-95C7-31727CFD33B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="36">
   <si>
     <t>順序</t>
   </si>
@@ -75,9 +75,6 @@
   </si>
   <si>
     <t>1</t>
-  </si>
-  <si>
-    <t>plains</t>
   </si>
   <si>
     <t>human</t>
@@ -611,13 +608,13 @@
         <v>13</v>
       </c>
       <c r="B2" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2" t="s">
         <v>17</v>
       </c>
-      <c r="C2" t="s">
-        <v>18</v>
-      </c>
       <c r="D2" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E2" s="2">
         <v>200</v>
@@ -645,22 +642,22 @@
     </row>
     <row r="3" spans="1:13" ht="15" customHeight="1">
       <c r="A3" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B3" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C3" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="C3" s="5" t="s">
-        <v>36</v>
-      </c>
       <c r="D3" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E3" s="2">
         <v>300</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G3" s="4">
         <v>200</v>
@@ -672,7 +669,7 @@
         <v>2.2000000000000002</v>
       </c>
       <c r="J3" s="4">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="K3" s="4">
         <v>1.6</v>
@@ -686,22 +683,22 @@
     </row>
     <row r="4" spans="1:13" ht="15" customHeight="1">
       <c r="A4" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="C4" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="C4" s="2" t="s">
-        <v>21</v>
-      </c>
       <c r="D4" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E4" s="2">
         <v>400</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G4" s="4">
         <v>300</v>
@@ -713,7 +710,7 @@
         <v>4.4000000000000004</v>
       </c>
       <c r="J4" s="4">
-        <v>2.8</v>
+        <v>3.5</v>
       </c>
       <c r="K4" s="4">
         <v>2.4</v>
@@ -727,22 +724,22 @@
     </row>
     <row r="5" spans="1:13" ht="15" customHeight="1">
       <c r="A5" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B5" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="C5" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="C5" s="2" t="s">
-        <v>24</v>
-      </c>
       <c r="D5" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E5" s="2">
         <v>500</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G5" s="4">
         <v>400</v>
@@ -751,10 +748,10 @@
         <v>0</v>
       </c>
       <c r="I5" s="4">
-        <v>6.5</v>
+        <v>10</v>
       </c>
       <c r="J5" s="4">
-        <v>3.8</v>
+        <v>5.5</v>
       </c>
       <c r="K5" s="4">
         <v>3.2</v>
@@ -768,22 +765,22 @@
     </row>
     <row r="6" spans="1:13" ht="15" customHeight="1">
       <c r="A6" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="C6" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="D6" s="2" t="s">
         <v>27</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>28</v>
       </c>
       <c r="E6" s="2">
         <v>600</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G6" s="4">
         <v>500</v>
@@ -792,10 +789,10 @@
         <v>11</v>
       </c>
       <c r="I6" s="4">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="J6" s="4">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="K6" s="4">
         <v>4</v>
@@ -809,22 +806,22 @@
     </row>
     <row r="7" spans="1:13" ht="15" customHeight="1">
       <c r="A7" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B7" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="C7" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="C7" s="2" t="s">
-        <v>31</v>
-      </c>
       <c r="D7" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E7" s="2">
         <v>700</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G7" s="4">
         <v>600</v>
@@ -833,10 +830,10 @@
         <v>11</v>
       </c>
       <c r="I7" s="4">
-        <v>25</v>
+        <v>60</v>
       </c>
       <c r="J7" s="4">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="K7" s="4">
         <v>8</v>
@@ -850,22 +847,22 @@
     </row>
     <row r="8" spans="1:13" ht="15" customHeight="1">
       <c r="A8" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B8" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="C8" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="C8" s="2" t="s">
-        <v>34</v>
-      </c>
       <c r="D8" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E8" s="2">
         <v>800</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G8" s="4">
         <v>700</v>
@@ -874,13 +871,13 @@
         <v>11</v>
       </c>
       <c r="I8" s="4">
-        <v>60</v>
+        <v>150</v>
       </c>
       <c r="J8" s="4">
+        <v>40</v>
+      </c>
+      <c r="K8" s="4">
         <v>20</v>
-      </c>
-      <c r="K8" s="4">
-        <v>15</v>
       </c>
       <c r="L8" s="4">
         <v>2.5</v>

--- a/config/Excel/Zones.xlsx
+++ b/config/Excel/Zones.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MyGame\Idle-RPG\claude\config\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9028C24C-2A1D-4702-95C7-31727CFD33B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D64B7DD4-6B4A-4B6A-BE0E-50160198C382}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -710,7 +710,7 @@
         <v>4.4000000000000004</v>
       </c>
       <c r="J4" s="4">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="K4" s="4">
         <v>2.4</v>
@@ -751,7 +751,7 @@
         <v>10</v>
       </c>
       <c r="J5" s="4">
-        <v>5.5</v>
+        <v>10</v>
       </c>
       <c r="K5" s="4">
         <v>3.2</v>
@@ -792,7 +792,7 @@
         <v>25</v>
       </c>
       <c r="J6" s="4">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="K6" s="4">
         <v>4</v>
@@ -833,7 +833,7 @@
         <v>60</v>
       </c>
       <c r="J7" s="4">
-        <v>15</v>
+        <v>45</v>
       </c>
       <c r="K7" s="4">
         <v>8</v>
@@ -874,7 +874,7 @@
         <v>150</v>
       </c>
       <c r="J8" s="4">
-        <v>40</v>
+        <v>100</v>
       </c>
       <c r="K8" s="4">
         <v>20</v>

--- a/config/Excel/Zones.xlsx
+++ b/config/Excel/Zones.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MyGame\Idle-RPG\claude\config\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D64B7DD4-6B4A-4B6A-BE0E-50160198C382}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11093B05-119E-4822-9947-2724A8E2F209}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -669,7 +669,7 @@
         <v>2.2000000000000002</v>
       </c>
       <c r="J3" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K3" s="4">
         <v>1.6</v>
@@ -707,13 +707,13 @@
         <v>0</v>
       </c>
       <c r="I4" s="4">
-        <v>4.4000000000000004</v>
+        <v>5</v>
       </c>
       <c r="J4" s="4">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="K4" s="4">
-        <v>2.4</v>
+        <v>3</v>
       </c>
       <c r="L4" s="4">
         <v>1.6</v>
@@ -748,13 +748,13 @@
         <v>0</v>
       </c>
       <c r="I5" s="4">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="J5" s="4">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="K5" s="4">
-        <v>3.2</v>
+        <v>4.5</v>
       </c>
       <c r="L5" s="4">
         <v>1.8</v>
@@ -789,13 +789,13 @@
         <v>11</v>
       </c>
       <c r="I6" s="4">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="J6" s="4">
-        <v>20</v>
+        <v>200</v>
       </c>
       <c r="K6" s="4">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="L6" s="4">
         <v>2</v>
@@ -830,13 +830,13 @@
         <v>11</v>
       </c>
       <c r="I7" s="4">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="J7" s="4">
-        <v>45</v>
+        <v>1000</v>
       </c>
       <c r="K7" s="4">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="L7" s="4">
         <v>2.2000000000000002</v>
@@ -871,13 +871,13 @@
         <v>11</v>
       </c>
       <c r="I8" s="4">
-        <v>150</v>
+        <v>400</v>
       </c>
       <c r="J8" s="4">
-        <v>100</v>
+        <v>8000</v>
       </c>
       <c r="K8" s="4">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="L8" s="4">
         <v>2.5</v>

--- a/config/Excel/Zones.xlsx
+++ b/config/Excel/Zones.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MyGame\Idle-RPG\claude\config\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11093B05-119E-4822-9947-2724A8E2F209}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E870A67-15FC-4A88-9B5B-8D7EA09D2937}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -148,6 +148,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="176" formatCode="0.0"/>
+  </numFmts>
   <fonts count="5">
     <font>
       <sz val="11"/>
@@ -217,7 +220,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -234,6 +237,9 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="1" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
@@ -241,14 +247,7 @@
   </cellStyles>
   <dxfs count="8">
     <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border outline="0">
-        <left style="thin">
-          <color rgb="FFD9E2F3"/>
-        </left>
-      </border>
-    </dxf>
-    <dxf>
+      <numFmt numFmtId="176" formatCode="0.0"/>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border outline="0">
         <left style="thin">
@@ -279,6 +278,14 @@
         <right style="thin">
           <color rgb="FFD9E2F3"/>
         </right>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border outline="0">
+        <left style="thin">
+          <color rgb="FFD9E2F3"/>
+        </left>
       </border>
     </dxf>
     <dxf>
@@ -343,10 +350,10 @@
     <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="前置通關關卡" dataDxfId="6"/>
     <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="最低轉生次數" dataDxfId="5"/>
     <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="生命倍率" dataDxfId="4"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="攻擊倍率" dataDxfId="3"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="防禦倍率" dataDxfId="2"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="攻擊倍率" dataDxfId="2"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="防禦倍率" dataDxfId="0"/>
     <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="攻速倍率" dataDxfId="1"/>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="經驗金幣獎勵倍率" dataDxfId="0"/>
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="經驗金幣獎勵倍率" dataDxfId="3"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -625,12 +632,12 @@
         <v>0</v>
       </c>
       <c r="I2" s="4">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="J2" s="4">
-        <v>1</v>
-      </c>
-      <c r="K2" s="4">
+        <v>0.8</v>
+      </c>
+      <c r="K2" s="6">
         <v>1</v>
       </c>
       <c r="L2" s="4">
@@ -666,12 +673,12 @@
         <v>0</v>
       </c>
       <c r="I3" s="4">
-        <v>2.2000000000000002</v>
+        <v>2.5</v>
       </c>
       <c r="J3" s="4">
         <v>3</v>
       </c>
-      <c r="K3" s="4">
+      <c r="K3" s="6">
         <v>1.6</v>
       </c>
       <c r="L3" s="4">
@@ -707,13 +714,13 @@
         <v>0</v>
       </c>
       <c r="I4" s="4">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J4" s="4">
         <v>10</v>
       </c>
-      <c r="K4" s="4">
-        <v>3</v>
+      <c r="K4" s="6">
+        <v>3.2</v>
       </c>
       <c r="L4" s="4">
         <v>1.6</v>
@@ -748,13 +755,13 @@
         <v>0</v>
       </c>
       <c r="I5" s="4">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="J5" s="4">
         <v>50</v>
       </c>
-      <c r="K5" s="4">
-        <v>4.5</v>
+      <c r="K5" s="6">
+        <v>10</v>
       </c>
       <c r="L5" s="4">
         <v>1.8</v>
@@ -789,13 +796,13 @@
         <v>11</v>
       </c>
       <c r="I6" s="4">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="J6" s="4">
         <v>200</v>
       </c>
-      <c r="K6" s="4">
-        <v>8</v>
+      <c r="K6" s="6">
+        <v>25</v>
       </c>
       <c r="L6" s="4">
         <v>2</v>
@@ -830,13 +837,13 @@
         <v>11</v>
       </c>
       <c r="I7" s="4">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="J7" s="4">
         <v>1000</v>
       </c>
-      <c r="K7" s="4">
-        <v>12</v>
+      <c r="K7" s="6">
+        <v>50</v>
       </c>
       <c r="L7" s="4">
         <v>2.2000000000000002</v>
@@ -871,13 +878,13 @@
         <v>11</v>
       </c>
       <c r="I8" s="4">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="J8" s="4">
         <v>8000</v>
       </c>
-      <c r="K8" s="4">
-        <v>25</v>
+      <c r="K8" s="6">
+        <v>100</v>
       </c>
       <c r="L8" s="4">
         <v>2.5</v>
